--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Confidential\MyDinnerDive\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\MyDinnerDive\dinner-dive-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C00738-C1B8-4B6B-8FB4-C1234FAB61E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CD8EC0-29F8-4C80-99D1-618E1128DC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21585" yWindow="4770" windowWidth="19725" windowHeight="10830" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="193">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -631,6 +620,14 @@
   </si>
   <si>
     <t>老闆只信三樣東西，鹽、柴魚和他的直覺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所屬群組ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1065,1134 +1062,1269 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="22.77734375" customWidth="1"/>
-    <col min="5" max="7" width="22.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.44140625" customWidth="1"/>
+    <col min="1" max="2" width="22.77734375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="22.77734375" customWidth="1"/>
+    <col min="6" max="8" width="22.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>174</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>179</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
       <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
       <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>181</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
       <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>184</v>
       </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
       <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
       <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
       <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
       <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
       <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>4</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>63</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>15</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>3</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1">
         <v>5</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>78</v>
       </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
       <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>83</v>
       </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
       <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>4</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
       <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>0</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>91</v>
       </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
         <v>93</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>33</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>98</v>
       </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>102</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>15</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
         <v>106</v>
       </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
       <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
         <v>107</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
         <v>110</v>
       </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
       <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <v>3</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>114</v>
       </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1">
         <v>5</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>117</v>
       </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>121</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>33</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>122</v>
       </c>
-      <c r="E33" s="1">
+      <c r="F33" s="1">
         <v>2</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I33" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
         <v>125</v>
       </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
       <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>127</v>
+      <c r="F34" s="1">
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>189</v>
       </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
       <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
         <v>128</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>131</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="1">
+      <c r="F36" s="1">
         <v>0</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
         <v>133</v>
       </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
       <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
         <v>134</v>
       </c>
-      <c r="E37" s="1">
+      <c r="F37" s="1">
         <v>0</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>136</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
         <v>139</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>33</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>140</v>
       </c>
-      <c r="E39" s="1">
+      <c r="F39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
         <v>144</v>
       </c>
-      <c r="C40" t="s">
-        <v>8</v>
-      </c>
       <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="1">
+      <c r="F40" s="1">
         <v>0</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
         <v>148</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>15</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>149</v>
       </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
         <v>152</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="1">
+      <c r="F42" s="1">
         <v>0</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
         <v>155</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>33</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>156</v>
       </c>
-      <c r="E43" s="1">
+      <c r="F43" s="1">
         <v>3</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>159</v>
       </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
       <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
         <v>163</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>164</v>
       </c>
-      <c r="E45" s="1">
+      <c r="F45" s="1">
         <v>4</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I45" t="s">
         <v>86</v>
       </c>
     </row>

--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\MyDinnerDive\dinner-dive-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CD8EC0-29F8-4C80-99D1-618E1128DC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802D8C8F-EFC0-41E8-8B5B-3D599FA99EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="195">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -628,6 +628,14 @@
   </si>
   <si>
     <t>所屬群組ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_display_order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群組顯示排序</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1062,16 +1070,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.77734375" style="1" customWidth="1"/>
-    <col min="3" max="5" width="22.77734375" customWidth="1"/>
-    <col min="6" max="8" width="22.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.44140625" customWidth="1"/>
+    <col min="1" max="3" width="22.77734375" style="1" customWidth="1"/>
+    <col min="4" max="6" width="22.77734375" customWidth="1"/>
+    <col min="7" max="9" width="22.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>166</v>
       </c>
@@ -1079,28 +1087,31 @@
         <v>192</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1108,1223 +1119,1355 @@
         <v>191</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>174</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>179</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
       <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
       <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>181</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
       <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
         <v>184</v>
       </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
       <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
       <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="4"/>
+      <c r="I10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
       <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
         <v>54</v>
       </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
       <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>4</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
         <v>59</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
         <v>68</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
         <v>72</v>
       </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="1">
         <v>5</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>2</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="D22" t="s">
-        <v>8</v>
-      </c>
       <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>2</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
         <v>83</v>
       </c>
-      <c r="D23" t="s">
-        <v>8</v>
-      </c>
       <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>4</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
         <v>87</v>
       </c>
-      <c r="D24" t="s">
-        <v>8</v>
-      </c>
       <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
         <v>91</v>
       </c>
-      <c r="D25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
         <v>93</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>33</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>2</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
         <v>98</v>
       </c>
-      <c r="D27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="1">
         <v>2</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
         <v>102</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>15</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
         <v>106</v>
       </c>
-      <c r="D29" t="s">
-        <v>8</v>
-      </c>
       <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
         <v>107</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="I29" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
         <v>110</v>
       </c>
-      <c r="D30" t="s">
-        <v>8</v>
-      </c>
       <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>3</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="I30" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
         <v>114</v>
       </c>
-      <c r="D31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="1">
         <v>5</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
         <v>117</v>
       </c>
-      <c r="D32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="I32" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
         <v>121</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>33</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>2</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J33" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
         <v>125</v>
       </c>
-      <c r="D34" t="s">
-        <v>8</v>
-      </c>
       <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>127</v>
+      <c r="G34" s="1">
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
         <v>189</v>
       </c>
-      <c r="D35" t="s">
-        <v>8</v>
-      </c>
       <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="I35" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
         <v>131</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>0</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
         <v>133</v>
       </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
       <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
         <v>134</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>0</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1">
+        <v>36</v>
+      </c>
+      <c r="D38" t="s">
         <v>136</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
         <v>139</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>33</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>140</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>2</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="I39" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
         <v>144</v>
       </c>
-      <c r="D40" t="s">
-        <v>8</v>
-      </c>
       <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
         <v>145</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="4"/>
+      <c r="I40" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
         <v>148</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>15</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="I41" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
         <v>152</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>33</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>153</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>0</v>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="4"/>
+      <c r="I42" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
         <v>155</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>33</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>3</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="I43" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
         <v>159</v>
       </c>
-      <c r="D44" t="s">
-        <v>8</v>
-      </c>
       <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
         <v>160</v>
       </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
         <v>163</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>15</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>164</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>4</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J45" t="s">
         <v>86</v>
       </c>
     </row>
